--- a/ExcelData/ItemMergeTable.xlsx
+++ b/ExcelData/ItemMergeTable.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Firefly\TapTapGame21\ExcelData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="18348" windowHeight="8100"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -90,13 +85,10 @@
     <t>结果物品状态</t>
   </si>
   <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Tree</t>
-  </si>
-  <si>
-    <t>BigTree</t>
+    <t>GamePlay.Core.Item_Water</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_Tree</t>
   </si>
 </sst>
 </file>
@@ -712,12 +704,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1031,9 +1026,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="8" width="17.2727272727273" customWidth="1"/>
+    <col min="2" max="8" width="17.2685185185185" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1118,53 +1113,37 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1">
-        <v>2</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1"/>
@@ -1437,7 +1416,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1449,7 +1428,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ExcelData/ItemMergeTable.xlsx
+++ b/ExcelData/ItemMergeTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18348" windowHeight="8100"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -89,6 +89,27 @@
   </si>
   <si>
     <t>GamePlay.Core.Item_Tree</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_Spore</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_Mushroom</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_ManEater</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_FernSeed</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_Fern</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_Thorn</t>
+  </si>
+  <si>
+    <t>GamePlay.Core.Item_Shovel</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1049,12 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="8" width="17.2685185185185" customWidth="1"/>
+    <col min="2" max="2" width="31.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="17.2685185185185" customWidth="1"/>
+    <col min="4" max="4" width="35.5555555555556" customWidth="1"/>
+    <col min="5" max="6" width="17.2685185185185" customWidth="1"/>
+    <col min="7" max="7" width="34.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="17.2685185185185" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1136,124 +1162,316 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>7</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>9</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1"/>
